--- a/fixtures/xlsx/multi-sheet/input.xlsx
+++ b/fixtures/xlsx/multi-sheet/input.xlsx
@@ -2,25 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="People" sheetId="1" r:id="rId1"/>
+    <sheet name="Products" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Alice</t>
+    <t>Widget</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Product</t>
   </si>
   <si>
-    <t>Bob</t>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -30,12 +39,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -47,12 +70,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>9.99</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/multi-sheet/input.xlsx
+++ b/fixtures/xlsx/multi-sheet/input.xlsx
@@ -11,16 +11,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Age</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Bob</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
   <si>
     <t>Widget</t>
@@ -39,15 +39,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -55,7 +55,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>25</v>

--- a/fixtures/xlsx/multi-sheet/input.xlsx
+++ b/fixtures/xlsx/multi-sheet/input.xlsx
@@ -11,13 +11,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Name</t>
+    <t>Alice</t>
   </si>
   <si>
     <t>Bob</t>
   </si>
   <si>
-    <t>Alice</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Age</t>
@@ -39,7 +39,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -47,7 +47,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>30</v>
